--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_528_Netherlands.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_528_Netherlands.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R1084af2f003d4b72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R48542f65457c45c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd3fec025e58f4e43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R0d3415a9523548c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R85026e313d874ae1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R908646000c48402d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rba7ca8602ffe4f0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re034a63f04bd4d78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rdd51e959a45d45bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Re442accb25624526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rd108c8c436e844d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R76f3c5b382414d69"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ528CommercialTable" displayName="EEZ528CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ528CommercialTable" displayName="EEZ528CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ528FunctionalTable" displayName="EEZ528FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ528FunctionalTable" displayName="EEZ528FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ528ValidationTable" displayName="EEZ528ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ528ValidationTable" displayName="EEZ528ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -12888,7 +12842,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73196fe44eb64f42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra81af40aa94d4905"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12898,20 +12852,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -12919,714 +12863,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>3.1109069236</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>3.1109069236</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$183,A2,'Species'!$U$2:$U$183))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>400.76244496867656</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>400.76244496867656</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>5869.317880056501</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.25805463966488</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1811.5679961411156</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>5869.317880056501</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1917.1440796943637</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$183,A3,'Species'!$U$2:$U$183))</x:f>
-        <x:v>11252328.025594594</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.25805463966488</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1811.5679961411156</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>10632668.430689177</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>619659.5949054174</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0582788411906918</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.05827884119069186</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>13347.3256181285</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.1683470616423035</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>147.34895549721088</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>13347.3256181285</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>151.09647126442047</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$183,A4,'Species'!$U$2:$U$183))</x:f>
-        <x:v>2016733.8017164161</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.1683470616423035</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>147.34895549721088</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1966714.488512399</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>50019.313204017235</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0254329306547445</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.02543293065474455</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>27758.4343506487</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3048370629354475</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>201.7609262174668</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>27758.4343506487</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>262.88312569988165</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$183,A5,'Species'!$U$2:$U$183))</x:f>
-        <x:v>7297223.986633494</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3048370629354475</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>201.7609262174668</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>5600567.424933627</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1696656.5616998663</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.302943689981551</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.302943689981551</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>22182.485742326797</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.1837716941546623</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>152.6763237519867</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>22182.485742326797</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>166.8774229619044</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$183,A6,'Species'!$U$2:$U$183))</x:f>
-        <x:v>3701756.0555686825</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.1837716941546623</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>152.6763237519867</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3386740.374819315</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>315015.68074936746</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0930144167800797</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.09301441678007981</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>8783.6747635139</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0937903091562116</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>12.410529440606643</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>8783.6747635139</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>38.578816400903044</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$183,A7,'Species'!$U$2:$U$183))</x:f>
-        <x:v>338863.7760268482</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0937903091562116</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>12.410529440606643</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>109010.05424930285</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>229853.72177754535</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>3.108555246214964</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>2.108555246214964</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>18814.810553427396</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3085822614179947</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>203.50836325036053</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>18814.810553427396</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>250.61903033135297</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$183,A8,'Species'!$U$2:$U$183))</x:f>
-        <x:v>4715349.576768081</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3085822614179947</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>203.50836325036053</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3828971.3005936192</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>886378.2761744615</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.231492535876945</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.23149253587694507</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1701.6757559103</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.593617110081313</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>392.2989177995826</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1701.6757559103</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>479.9841072631435</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$183,A9,'Species'!$U$2:$U$183))</x:f>
-        <x:v>816777.3185519403</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.593617110081313</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>392.2989177995826</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>667565.5574893975</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>149211.7610625428</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.223516266512765</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.22351626651276513</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>10.112061075600002</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.4416869378884734</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>276.49478082914464</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>10.112061075600002</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>284.56161763986285</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$183,A10,'Species'!$U$2:$U$183))</x:f>
-        <x:v>2877.504457345828</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.4416869378884734</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>276.49478082914464</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2795.9321108289473</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>81.57234651688077</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0291753673849742</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.02917536738497414</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1637.6099620132</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.896176347605331</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>787.3654387554685</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1637.6099620132</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>800.8932181528867</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$183,A11,'Species'!$U$2:$U$183))</x:f>
-        <x:v>1311550.7125559782</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.896176347605331</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>787.3654387554685</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1289397.4862508492</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>22153.226305129007</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0171810683217193</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.017181068321719336</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>982.1616555362999</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.9390611758027365</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>869.0828418387939</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>982.1616555362999</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>940.6852563197315</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$183,A12,'Species'!$U$2:$U$183))</x:f>
-        <x:v>923904.9886855761</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.9390611758027365</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>869.0828418387939</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>853579.8427385822</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>70325.14594699396</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.082388480170017</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.08238848017001706</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>14.0373818371</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.386358228259711</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2434.211042744337</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>14.0373818371</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2447.165967101644</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$183,A13,'Species'!$U$2:$U$183))</x:f>
-        <x:v>34351.80309896188</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.386358228259711</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2434.211042744337</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>34169.94987908761</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>181.8532198742687</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0053220218501275</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.005322021850127585</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3892d356c2ea4cab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1b4bdbfe3274004"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13636,20 +13116,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13657,1416 +13127,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>547.4112054123999</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.06110292533953</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1151.07315445813</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>547.4112054123999</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1255.6032998657226</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$183,A2,'Species'!$U$2:$U$183))</x:f>
-        <x:v>687331.3158992822</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.06110292533953</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1151.07315445813</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>630110.3429997785</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>57220.97289950377</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0908110357736565</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.09081103577365637</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>167.7955768452</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.417393150304625</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2614.5271155468095</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>167.7955768452</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2629.3734817785216</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$183,A3,'Species'!$U$2:$U$183))</x:f>
-        <x:v>441197.240116499</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.417393150304625</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2614.5271155468095</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>438706.08553059376</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>2491.1545859052567</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0056784135622197</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.00567841356221974</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.0005551299</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.92</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>831.7637711026708</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.0005551299</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$183,A4,'Species'!$U$2:$U$183))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>0.46173693907584856</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.92</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>0.46173693907584856</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1500.2905642822</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.095701229952521</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1246.5256800198065</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1500.2905642822</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1251.745037843988</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$183,A5,'Species'!$U$2:$U$183))</x:f>
-        <x:v>1877981.2691644006</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.095701229952521</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1246.5256800198065</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1870150.7158691685</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>7830.553295232123</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0041871241867224</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0041871241867224625</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>347.3684561231</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.0744825856061535</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1187.0871001238984</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>347.3684561231</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1472.6082562076888</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$183,A6,'Species'!$U$2:$U$183))</x:f>
-        <x:v>511537.6564329953</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.0744825856061535</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1187.0871001238984</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>412356.6132536864</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>99181.04317930888</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.2405224991948693</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.24052249919486945</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>13430.9065014597</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3119144382199965</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>205.07581124431422</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>13430.9065014597</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>281.499388087801</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$183,A7,'Species'!$U$2:$U$183))</x:f>
-        <x:v>3780791.9616253735</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3119144382199965</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>205.07581124431422</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2754354.046533382</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1026437.9150919914</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3726601220289243</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.37266012202892423</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.20015500619999999</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.034801748645945</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1083.4322244794594</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.20015500619999999</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1089.847433378484</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$183,A8,'Species'!$U$2:$U$183))</x:f>
-        <x:v>218.13841978492454</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.034801748645945</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1083.4322244794594</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>216.85438360796596</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1.2840361769585797</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0059211907806296</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.005921190780629494</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>279.0848643114</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.882560309969292</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>763.0628494540998</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>279.0848643114</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>822.312819531226</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$183,A9,'Species'!$U$2:$U$183))</x:f>
-        <x:v>229495.06166039695</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.882560309969292</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>763.0628494540998</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>212959.29180096768</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>16535.769859429274</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0776475622152408</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.07764756221524087</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>156.6694297936</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.2856347508258827</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>193.03441812912558</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>156.6694297936</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>194.5524980373364</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$183,A10,'Species'!$U$2:$U$183))</x:f>
-        <x:v>30480.428932429975</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.2856347508258827</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>193.03441812912558</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>30242.592218829464</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>237.83671360051085</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0078642965483768</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.007864296548376906</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>356.3153774567</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.086589749480033</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1220.6460482850007</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>356.3153774567</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1284.8716833966623</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$183,A11,'Species'!$U$2:$U$183))</x:f>
-        <x:v>457819.53885290725</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.086589749480033</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1220.6460482850007</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>434934.95743569924</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>22884.581417208014</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.05261610046737</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.052616100467369926</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1958.1865588088</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.0608912117815543</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>115.05121563039035</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1958.1865588088</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>133.0653819930084</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$183,A12,'Species'!$U$2:$U$183))</x:f>
-        <x:v>260566.84246146758</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.0608912117815543</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>115.05121563039035</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>225291.7440220433</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>35275.09843942427</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1565751936119453</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.15657519361194538</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>92.68490982430001</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.459988673096764</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2883.956285224626</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>92.68490982430001</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2884.0043577500346</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$183,A13,'Species'!$U$2:$U$183))</x:f>
-        <x:v>267303.68383095023</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.459988673096764</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2883.956285224626</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>267299.22823326767</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>4.455597682564985</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0000166689507934</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.000016668950793515416</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>0.7518795789</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>0.7518795789</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$183,A14,'Species'!$U$2:$U$183))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>903.9580768265872</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>903.9580768265872</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>3893.2943444732005</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>4.332508474339804</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>2150.3466384050857</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>3893.2943444732005</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>2216.947537695787</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$183,A15,'Species'!$U$2:$U$183))</x:f>
-        <x:v>8631229.310504796</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>4.332508474339804</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>2150.3466384050857</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>8371932.405959479</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>259296.9045453174</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0309721689058</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.03097216890579998</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>19956.6977764599</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.3431395722372304</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>220.36345466222636</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>19956.6977764599</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>252.92128144674965</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$183,A16,'Species'!$U$2:$U$183))</x:f>
-        <x:v>5047473.575067737</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.3431395722372304</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>220.36345466222636</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>4397726.8656706745</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>649746.7093970627</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.1477460354505151</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.14774603545051523</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>11377.8504523545</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.4070855557879822</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>255.32042330325262</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>11377.8504523545</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>271.98148214063536</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$183,A17,'Species'!$U$2:$U$183))</x:f>
-        <x:v>3094564.6296058754</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.4070855557879822</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>255.32042330325262</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2904997.5937762554</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>189567.03582961997</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.065255488071919</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.06525548807191905</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>9.802993840800001</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.3330991812311</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>215.32734285729262</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>9.802993840800001</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>229.59025882173174</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$183,A18,'Species'!$U$2:$U$183))</x:f>
-        <x:v>2250.6718931371142</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.3330991812311</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>215.32734285729262</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>2110.8526157858696</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>139.81927735124464</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0662382945666673</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0662382945666673</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>9164.5458697679</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.125918410485176</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>13.36344438208462</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>9164.5458697679</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>40.42194509348832</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$183,A19,'Species'!$U$2:$U$183))</x:f>
-        <x:v>370448.76995451323</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.125918410485176</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>13.36344438208462</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>122469.89901770666</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>247978.87093680658</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>3.024814855942307</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>2.024814855942307</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>11389.1390593197</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.186822435396787</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>153.7525882620388</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>11389.1390593197</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>154.19663857891723</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$183,A20,'Species'!$U$2:$U$183))</x:f>
-        <x:v>1756166.959254949</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.186822435396787</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>153.7525882620388</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1751109.6084466858</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>5057.350808263058</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0028880835236518</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.002888083523651703</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>0.005033617</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.08</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>120.22644346174131</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>0.005033617</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>120.22644346174131</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$183,A21,'Species'!$U$2:$U$183))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>0.6051738696585599</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.08</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>120.22644346174131</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>0.6051738696585599</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>11801.442288958999</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.0111305686247123</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>102.59603301108861</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>11801.442288958999</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>102.64232972571632</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$183,A22,'Species'!$U$2:$U$183))</x:f>
-        <x:v>1211327.530662342</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.0111305686247123</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>102.59603301108861</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>1210781.1626564944</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>546.3680058475584</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0004512524828588</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.00045125248285892447</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>0.0235156163</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.369227737101664</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>234.0064009236869</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>0.0235156163</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>267.4646046745524</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$183,A23,'Species'!$U$2:$U$183))</x:f>
-        <x:v>6.28959501735796</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.369227737101664</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>234.0064009236869</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>5.502804735865387</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0.7867902814925731</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.1429798655882781</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.1429798655882781</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>14327.527849189</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.298202592095599</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>198.7021618045396</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>14327.527849189</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>245.4318750605092</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$183,A24,'Species'!$U$2:$U$183))</x:f>
-        <x:v>3516432.025008121</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.298202592095599</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>198.7021618045396</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>2846910.7569486</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>669521.268059521</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.2351746595587467</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.23517465955874672</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>144.0289267544</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.845071512518228</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>699.9572440339823</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>144.0289267544</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>702.9795375049911</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$183,A25,'Species'!$U$2:$U$183))</x:f>
-        <x:v>101249.38831714835</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.845071512518228</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>699.9572440339823</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>100814.09063218212</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>435.29768496622273</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0043178258340335</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.004317825834033421</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>202.7324870138</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.824324100582953</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>667.3045722728942</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>202.7324870138</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>667.5841738473343</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$183,A26,'Species'!$U$2:$U$183))</x:f>
-        <x:v>135340.9998551231</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.824324100582953</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>667.3045722728942</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>135284.3155325639</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>56.684322559216525</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.000419001436612</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.0004190014366120085</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3324ce5206184700"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7d39ca6aa0849ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15241,7 +13792,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -15340,7 +13891,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>32412118.312102888</x:v>
+        <x:v>28372581.604711153</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15354,7 +13905,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>32412118.312102884</x:v>
+        <x:v>29121670.551329825</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15368,7 +13919,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-4039536.707391735</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15382,7 +13933,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-3.725290298461914e-9</x:v>
+        <x:v>-3290447.7607730627</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15393,9 +13944,9 @@
         <x:v>EEZ_528</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -15407,47 +13958,19 @@
         <x:v>EEZ_528</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_528</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_528</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra488092b34804966"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R669c880bdc9c4f74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15494,7 +14017,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
